--- a/Assets/04. Bakery Factory/WeaponsData.xlsx
+++ b/Assets/04. Bakery Factory/WeaponsData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Unity Project\EnhancingTheSword\Assets\StreamingAssets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Unity Project\EnhancingTheSword\Assets\04. Bakery Factory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65675FA3-55D1-4C76-927D-2C5B3B6ADE24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6051CF96-35ED-49C1-AFF4-5A6D29B59210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1890" windowWidth="28800" windowHeight="15435" xr2:uid="{E3D72ED6-2DDD-4572-81DB-8F3E5E991BAA}"/>
+    <workbookView xWindow="480" yWindow="1470" windowWidth="28800" windowHeight="15435" xr2:uid="{E3D72ED6-2DDD-4572-81DB-8F3E5E991BAA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,14 +36,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
-    <t>Name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Price</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>목검</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -60,10 +52,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>probability</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>EnhancingPrice</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -210,6 +198,18 @@
   </si>
   <si>
     <t>Index</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeaponName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeaponPrice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Probability</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -587,25 +587,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" t="s">
         <v>47</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>6</v>
-      </c>
       <c r="E1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -613,7 +613,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <v>10000</v>
@@ -625,7 +625,7 @@
         <v>1000</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -633,19 +633,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3">
         <v>180000</v>
       </c>
       <c r="D3">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E3">
         <v>9000</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -653,19 +653,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4">
         <v>400000</v>
       </c>
       <c r="D4">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E4">
         <v>20000</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -673,19 +673,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C5">
         <v>1000000</v>
       </c>
       <c r="D5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E5">
         <v>70000</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -693,7 +693,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C6">
         <v>2000000</v>
@@ -705,7 +705,7 @@
         <v>120000</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -713,19 +713,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C7">
         <v>2800000</v>
       </c>
       <c r="D7">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E7">
         <v>180000</v>
       </c>
       <c r="F7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -733,19 +733,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C8">
         <v>3200000</v>
       </c>
       <c r="D8">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E8">
         <v>240000</v>
       </c>
       <c r="F8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -753,7 +753,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C9">
         <v>3500000</v>
@@ -765,7 +765,7 @@
         <v>300000</v>
       </c>
       <c r="F9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -773,19 +773,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C10">
         <v>4500000</v>
       </c>
       <c r="D10">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E10">
         <v>380000</v>
       </c>
       <c r="F10" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -793,19 +793,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>7000000</v>
       </c>
       <c r="D11">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="E11">
         <v>650000</v>
       </c>
       <c r="F11" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -813,7 +813,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C12">
         <v>18000000</v>
@@ -825,7 +825,7 @@
         <v>1500000</v>
       </c>
       <c r="F12" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -833,19 +833,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C13">
         <v>35000000</v>
       </c>
       <c r="D13">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E13">
         <v>2800000</v>
       </c>
       <c r="F13" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -853,7 +853,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C14">
         <v>90000000</v>
@@ -865,7 +865,7 @@
         <v>7000000</v>
       </c>
       <c r="F14" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -873,22 +873,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C15">
         <v>105000000</v>
       </c>
       <c r="D15">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E15">
         <v>9500000</v>
       </c>
       <c r="F15" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G15" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -896,7 +896,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C16">
         <v>125200000</v>
@@ -908,7 +908,7 @@
         <v>12000000</v>
       </c>
       <c r="F16" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -916,19 +916,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C17">
         <v>160000000</v>
       </c>
       <c r="D17">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E17">
         <v>22000000</v>
       </c>
       <c r="F17" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G17">
         <v>14</v>
@@ -939,7 +939,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C18">
         <v>220000000</v>
@@ -951,7 +951,7 @@
         <v>36000000</v>
       </c>
       <c r="F18" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -959,19 +959,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C19">
         <v>500000000</v>
       </c>
       <c r="D19">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E19">
         <v>90000000</v>
       </c>
       <c r="F19" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -979,7 +979,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C20">
         <v>1500000000</v>
@@ -991,7 +991,7 @@
         <v>22000000</v>
       </c>
       <c r="F20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -999,7 +999,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C21">
         <v>4500000000</v>
@@ -1011,7 +1011,7 @@
         <v>60000000</v>
       </c>
       <c r="F21" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/04. Bakery Factory/WeaponsData.xlsx
+++ b/Assets/04. Bakery Factory/WeaponsData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Unity Project\EnhancingTheSword\Assets\04. Bakery Factory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6051CF96-35ED-49C1-AFF4-5A6D29B59210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{412B2046-8CEE-4564-90B2-35150A782E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="1470" windowWidth="28800" windowHeight="15435" xr2:uid="{E3D72ED6-2DDD-4572-81DB-8F3E5E991BAA}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="28800" windowHeight="15435" xr2:uid="{E3D72ED6-2DDD-4572-81DB-8F3E5E991BAA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t>목검</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -211,6 +211,15 @@
   <si>
     <t>Probability</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WarInfluence</t>
+  </si>
+  <si>
+    <t>InfuenceDuration</t>
+  </si>
+  <si>
+    <t>DeliveryTime</t>
   </si>
 </sst>
 </file>
@@ -574,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3947DBD-8943-41C3-BAD8-45FA12CDB025}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26.375" customWidth="1"/>
@@ -583,9 +592,12 @@
     <col min="5" max="5" width="13.75" customWidth="1"/>
     <col min="6" max="6" width="27.125" customWidth="1"/>
     <col min="7" max="7" width="18.25" customWidth="1"/>
+    <col min="8" max="8" width="14.875" customWidth="1"/>
+    <col min="9" max="9" width="12.375" customWidth="1"/>
+    <col min="10" max="10" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>44</v>
       </c>
@@ -605,10 +617,19 @@
         <v>12</v>
       </c>
       <c r="G1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -627,8 +648,17 @@
       <c r="F2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G2">
+        <v>0.5</v>
+      </c>
+      <c r="H2">
+        <v>10</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -647,8 +677,17 @@
       <c r="F3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>12</v>
+      </c>
+      <c r="I3">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -667,8 +706,17 @@
       <c r="F4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G4">
+        <v>1.5</v>
+      </c>
+      <c r="H4">
+        <v>15</v>
+      </c>
+      <c r="I4">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -687,8 +735,17 @@
       <c r="F5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>20</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -707,8 +764,17 @@
       <c r="F6" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>20</v>
+      </c>
+      <c r="I6">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -727,8 +793,17 @@
       <c r="F7" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>20</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -747,8 +822,17 @@
       <c r="F8" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G8">
+        <v>4</v>
+      </c>
+      <c r="H8">
+        <v>25</v>
+      </c>
+      <c r="I8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -767,8 +851,17 @@
       <c r="F9" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9">
+        <v>25</v>
+      </c>
+      <c r="I9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -787,8 +880,17 @@
       <c r="F10" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G10">
+        <v>7</v>
+      </c>
+      <c r="H10">
+        <v>25</v>
+      </c>
+      <c r="I10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -807,8 +909,17 @@
       <c r="F11" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G11">
+        <v>10</v>
+      </c>
+      <c r="H11">
+        <v>60</v>
+      </c>
+      <c r="I11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -827,8 +938,17 @@
       <c r="F12" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G12">
+        <v>15</v>
+      </c>
+      <c r="H12">
+        <v>62.5</v>
+      </c>
+      <c r="I12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -847,8 +967,17 @@
       <c r="F13" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G13">
+        <v>20</v>
+      </c>
+      <c r="H13">
+        <v>65</v>
+      </c>
+      <c r="I13">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -867,8 +996,17 @@
       <c r="F14" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G14">
+        <v>30</v>
+      </c>
+      <c r="H14">
+        <v>70</v>
+      </c>
+      <c r="I14">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -887,11 +1025,20 @@
       <c r="F15" t="s">
         <v>36</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15">
+        <v>40</v>
+      </c>
+      <c r="H15">
+        <v>80</v>
+      </c>
+      <c r="I15">
+        <v>60</v>
+      </c>
+      <c r="J15" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -910,8 +1057,17 @@
       <c r="F16" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G16">
+        <v>50</v>
+      </c>
+      <c r="H16">
+        <v>90</v>
+      </c>
+      <c r="I16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -931,10 +1087,19 @@
         <v>38</v>
       </c>
       <c r="G17">
+        <v>65</v>
+      </c>
+      <c r="H17">
+        <v>95</v>
+      </c>
+      <c r="I17">
+        <v>115</v>
+      </c>
+      <c r="J17">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -953,8 +1118,17 @@
       <c r="F18" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G18">
+        <v>80</v>
+      </c>
+      <c r="H18">
+        <v>100</v>
+      </c>
+      <c r="I18">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -973,8 +1147,17 @@
       <c r="F19" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G19">
+        <v>130</v>
+      </c>
+      <c r="H19">
+        <v>130</v>
+      </c>
+      <c r="I19">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -993,8 +1176,17 @@
       <c r="F20" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G20">
+        <v>250</v>
+      </c>
+      <c r="H20">
+        <v>150</v>
+      </c>
+      <c r="I20">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1012,6 +1204,15 @@
       </c>
       <c r="F21" t="s">
         <v>42</v>
+      </c>
+      <c r="G21">
+        <v>500</v>
+      </c>
+      <c r="H21">
+        <v>200</v>
+      </c>
+      <c r="I21">
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/04. Bakery Factory/WeaponsData.xlsx
+++ b/Assets/04. Bakery Factory/WeaponsData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Unity Project\EnhancingTheSword\Assets\04. Bakery Factory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{412B2046-8CEE-4564-90B2-35150A782E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{705FC4A5-FD5B-4628-A214-A5AF8A556751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="780" windowWidth="28800" windowHeight="15435" xr2:uid="{E3D72ED6-2DDD-4572-81DB-8F3E5E991BAA}"/>
   </bookViews>
@@ -216,10 +216,11 @@
     <t>WarInfluence</t>
   </si>
   <si>
-    <t>InfuenceDuration</t>
-  </si>
-  <si>
     <t>DeliveryTime</t>
+  </si>
+  <si>
+    <t>InfluenceDuration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -620,10 +621,10 @@
         <v>48</v>
       </c>
       <c r="H1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1" t="s">
         <v>49</v>
-      </c>
-      <c r="I1" t="s">
-        <v>50</v>
       </c>
       <c r="J1" t="s">
         <v>43</v>

--- a/Assets/04. Bakery Factory/WeaponsData.xlsx
+++ b/Assets/04. Bakery Factory/WeaponsData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Unity Project\EnhancingTheSword\Assets\04. Bakery Factory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{705FC4A5-FD5B-4628-A214-A5AF8A556751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7A02E5-7D21-4CEF-B540-0D442E15A891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="28800" windowHeight="15435" xr2:uid="{E3D72ED6-2DDD-4572-81DB-8F3E5E991BAA}"/>
+    <workbookView xWindow="5850" yWindow="5040" windowWidth="28800" windowHeight="15435" xr2:uid="{E3D72ED6-2DDD-4572-81DB-8F3E5E991BAA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1172,7 +1172,7 @@
         <v>30</v>
       </c>
       <c r="E20">
-        <v>22000000</v>
+        <v>220000000</v>
       </c>
       <c r="F20" t="s">
         <v>41</v>
@@ -1201,7 +1201,7 @@
         <v>10</v>
       </c>
       <c r="E21">
-        <v>60000000</v>
+        <v>600000000</v>
       </c>
       <c r="F21" t="s">
         <v>42</v>

--- a/Assets/04. Bakery Factory/WeaponsData.xlsx
+++ b/Assets/04. Bakery Factory/WeaponsData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Unity Project\EnhancingTheSword\Assets\04. Bakery Factory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7A02E5-7D21-4CEF-B540-0D442E15A891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84509F99-55A9-447A-9BFC-5730EDB12C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5850" yWindow="5040" windowWidth="28800" windowHeight="15435" xr2:uid="{E3D72ED6-2DDD-4572-81DB-8F3E5E991BAA}"/>
+    <workbookView xWindow="8220" yWindow="1095" windowWidth="28770" windowHeight="15435" xr2:uid="{E3D72ED6-2DDD-4572-81DB-8F3E5E991BAA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -584,21 +584,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3947DBD-8943-41C3-BAD8-45FA12CDB025}">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26.375" customWidth="1"/>
-    <col min="3" max="3" width="16.125" customWidth="1"/>
-    <col min="4" max="4" width="10.75" customWidth="1"/>
-    <col min="5" max="5" width="13.75" customWidth="1"/>
-    <col min="6" max="6" width="27.125" customWidth="1"/>
-    <col min="7" max="7" width="18.25" customWidth="1"/>
-    <col min="8" max="8" width="14.875" customWidth="1"/>
-    <col min="9" max="9" width="12.375" customWidth="1"/>
-    <col min="10" max="10" width="11.5" customWidth="1"/>
+    <col min="3" max="4" width="16.125" customWidth="1"/>
+    <col min="5" max="5" width="10.75" customWidth="1"/>
+    <col min="6" max="7" width="13.75" customWidth="1"/>
+    <col min="8" max="8" width="27.125" customWidth="1"/>
+    <col min="9" max="9" width="18.25" customWidth="1"/>
+    <col min="10" max="10" width="14.875" customWidth="1"/>
+    <col min="11" max="11" width="12.375" customWidth="1"/>
+    <col min="12" max="12" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>44</v>
       </c>
@@ -608,29 +608,29 @@
       <c r="C1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>48</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>50</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>49</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -640,26 +640,46 @@
       <c r="C2">
         <v>10000</v>
       </c>
-      <c r="D2">
-        <v>100</v>
+      <c r="D2" t="str">
+        <f>IF(C2&gt;=100000000,
+   INT(C2/100000000)&amp;"억"&amp;
+   IF(INT(MOD(C2,100000000)/10000)&lt;&gt;0," "&amp;INT(MOD(C2,100000000)/10000)&amp;"만","")&amp;
+   IF(MOD(C2,10000)&lt;&gt;0," "&amp;MOD(C2,10000),""),
+   IF(INT(C2/10000)&lt;&gt;0,INT(C2/10000)&amp;"만","")&amp;
+   IF(MOD(C2,10000)&lt;&gt;0," "&amp;MOD(C2,10000),"")
+)</f>
+        <v>1만</v>
       </c>
       <c r="E2">
+        <v>95</v>
+      </c>
+      <c r="F2">
         <v>1000</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="str">
+        <f>IF(F2&gt;=100000000,
+   INT(F2/100000000)&amp;"억"&amp;
+   IF(INT(MOD(F2,100000000)/10000)&lt;&gt;0," "&amp;INT(MOD(F2,100000000)/10000)&amp;"만","")&amp;
+   IF(MOD(F2,10000)&lt;&gt;0," "&amp;MOD(F2,10000),""),
+   IF(INT(F2/10000)&lt;&gt;0,INT(F2/10000)&amp;"만","")&amp;
+   IF(MOD(F2,10000)&lt;&gt;0," "&amp;MOD(F2,10000),"")
+)</f>
+        <v xml:space="preserve"> 1000</v>
+      </c>
+      <c r="H2" t="s">
         <v>23</v>
       </c>
-      <c r="G2">
+      <c r="I2">
         <v>0.5</v>
       </c>
-      <c r="H2">
+      <c r="J2">
         <v>10</v>
       </c>
-      <c r="I2">
+      <c r="K2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -669,26 +689,46 @@
       <c r="C3">
         <v>180000</v>
       </c>
-      <c r="D3">
-        <v>99</v>
+      <c r="D3" t="str">
+        <f t="shared" ref="D3:D21" si="0">IF(C3&gt;=100000000,
+   INT(C3/100000000)&amp;"억"&amp;
+   IF(INT(MOD(C3,100000000)/10000)&lt;&gt;0," "&amp;INT(MOD(C3,100000000)/10000)&amp;"만","")&amp;
+   IF(MOD(C3,10000)&lt;&gt;0," "&amp;MOD(C3,10000),""),
+   IF(INT(C3/10000)&lt;&gt;0,INT(C3/10000)&amp;"만","")&amp;
+   IF(MOD(C3,10000)&lt;&gt;0," "&amp;MOD(C3,10000),"")
+)</f>
+        <v>18만</v>
       </c>
       <c r="E3">
+        <v>90</v>
+      </c>
+      <c r="F3">
         <v>9000</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="str">
+        <f t="shared" ref="G3:G21" si="1">IF(F3&gt;=100000000,
+   INT(F3/100000000)&amp;"억"&amp;
+   IF(INT(MOD(F3,100000000)/10000)&lt;&gt;0," "&amp;INT(MOD(F3,100000000)/10000)&amp;"만","")&amp;
+   IF(MOD(F3,10000)&lt;&gt;0," "&amp;MOD(F3,10000),""),
+   IF(INT(F3/10000)&lt;&gt;0,INT(F3/10000)&amp;"만","")&amp;
+   IF(MOD(F3,10000)&lt;&gt;0," "&amp;MOD(F3,10000),"")
+)</f>
+        <v xml:space="preserve"> 9000</v>
+      </c>
+      <c r="H3" t="s">
         <v>24</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>1</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>12</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>1.2</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -698,26 +738,34 @@
       <c r="C4">
         <v>400000</v>
       </c>
-      <c r="D4">
-        <v>97</v>
+      <c r="D4" t="str">
+        <f t="shared" si="0"/>
+        <v>40만</v>
       </c>
       <c r="E4">
+        <v>85</v>
+      </c>
+      <c r="F4">
         <v>20000</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="str">
+        <f t="shared" si="1"/>
+        <v>2만</v>
+      </c>
+      <c r="H4" t="s">
         <v>25</v>
-      </c>
-      <c r="G4">
-        <v>1.5</v>
-      </c>
-      <c r="H4">
-        <v>15</v>
       </c>
       <c r="I4">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J4">
+        <v>15</v>
+      </c>
+      <c r="K4">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -727,26 +775,34 @@
       <c r="C5">
         <v>1000000</v>
       </c>
-      <c r="D5">
-        <v>95</v>
+      <c r="D5" t="str">
+        <f t="shared" si="0"/>
+        <v>100만</v>
       </c>
       <c r="E5">
+        <v>83</v>
+      </c>
+      <c r="F5">
         <v>70000</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="str">
+        <f t="shared" si="1"/>
+        <v>7만</v>
+      </c>
+      <c r="H5" t="s">
         <v>26</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>20</v>
       </c>
       <c r="I5">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J5">
+        <v>20</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -756,26 +812,34 @@
       <c r="C6">
         <v>2000000</v>
       </c>
-      <c r="D6">
-        <v>90</v>
+      <c r="D6" t="str">
+        <f t="shared" si="0"/>
+        <v>200만</v>
       </c>
       <c r="E6">
+        <v>80</v>
+      </c>
+      <c r="F6">
         <v>120000</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="str">
+        <f t="shared" si="1"/>
+        <v>12만</v>
+      </c>
+      <c r="H6" t="s">
         <v>27</v>
       </c>
-      <c r="G6">
+      <c r="I6">
         <v>3</v>
       </c>
-      <c r="H6">
+      <c r="J6">
         <v>20</v>
       </c>
-      <c r="I6">
+      <c r="K6">
         <v>2.5</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -785,26 +849,34 @@
       <c r="C7">
         <v>2800000</v>
       </c>
-      <c r="D7">
-        <v>85</v>
+      <c r="D7" t="str">
+        <f t="shared" si="0"/>
+        <v>280만</v>
       </c>
       <c r="E7">
+        <v>78</v>
+      </c>
+      <c r="F7">
         <v>180000</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="str">
+        <f t="shared" si="1"/>
+        <v>18만</v>
+      </c>
+      <c r="H7" t="s">
         <v>28</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>20</v>
       </c>
       <c r="I7">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J7">
+        <v>20</v>
+      </c>
+      <c r="K7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -814,26 +886,34 @@
       <c r="C8">
         <v>3200000</v>
       </c>
-      <c r="D8">
-        <v>83</v>
+      <c r="D8" t="str">
+        <f t="shared" si="0"/>
+        <v>320만</v>
       </c>
       <c r="E8">
+        <v>75</v>
+      </c>
+      <c r="F8">
         <v>240000</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="str">
+        <f t="shared" si="1"/>
+        <v>24만</v>
+      </c>
+      <c r="H8" t="s">
         <v>29</v>
       </c>
-      <c r="G8">
+      <c r="I8">
         <v>4</v>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>25</v>
       </c>
-      <c r="I8">
+      <c r="K8">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -843,26 +923,34 @@
       <c r="C9">
         <v>3500000</v>
       </c>
-      <c r="D9">
-        <v>80</v>
+      <c r="D9" t="str">
+        <f t="shared" si="0"/>
+        <v>350만</v>
       </c>
       <c r="E9">
+        <v>70</v>
+      </c>
+      <c r="F9">
         <v>300000</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="str">
+        <f t="shared" si="1"/>
+        <v>30만</v>
+      </c>
+      <c r="H9" t="s">
         <v>30</v>
       </c>
-      <c r="G9">
+      <c r="I9">
         <v>5</v>
       </c>
-      <c r="H9">
+      <c r="J9">
         <v>25</v>
       </c>
-      <c r="I9">
+      <c r="K9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -872,26 +960,34 @@
       <c r="C10">
         <v>4500000</v>
       </c>
-      <c r="D10">
-        <v>78</v>
+      <c r="D10" t="str">
+        <f t="shared" si="0"/>
+        <v>450만</v>
       </c>
       <c r="E10">
+        <v>67</v>
+      </c>
+      <c r="F10">
         <v>380000</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="str">
+        <f t="shared" si="1"/>
+        <v>38만</v>
+      </c>
+      <c r="H10" t="s">
         <v>31</v>
       </c>
-      <c r="G10">
+      <c r="I10">
         <v>7</v>
       </c>
-      <c r="H10">
+      <c r="J10">
         <v>25</v>
       </c>
-      <c r="I10">
+      <c r="K10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -901,26 +997,34 @@
       <c r="C11">
         <v>7000000</v>
       </c>
-      <c r="D11">
-        <v>75</v>
+      <c r="D11" t="str">
+        <f t="shared" si="0"/>
+        <v>700만</v>
       </c>
       <c r="E11">
+        <v>65</v>
+      </c>
+      <c r="F11">
         <v>650000</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="str">
+        <f t="shared" si="1"/>
+        <v>65만</v>
+      </c>
+      <c r="H11" t="s">
         <v>32</v>
       </c>
-      <c r="G11">
+      <c r="I11">
         <v>10</v>
       </c>
-      <c r="H11">
+      <c r="J11">
         <v>60</v>
       </c>
-      <c r="I11">
+      <c r="K11">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -930,26 +1034,34 @@
       <c r="C12">
         <v>18000000</v>
       </c>
-      <c r="D12">
-        <v>70</v>
+      <c r="D12" t="str">
+        <f t="shared" si="0"/>
+        <v>1800만</v>
       </c>
       <c r="E12">
+        <v>60</v>
+      </c>
+      <c r="F12">
         <v>1500000</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="str">
+        <f t="shared" si="1"/>
+        <v>150만</v>
+      </c>
+      <c r="H12" t="s">
         <v>33</v>
       </c>
-      <c r="G12">
+      <c r="I12">
         <v>15</v>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>62.5</v>
       </c>
-      <c r="I12">
+      <c r="K12">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -957,28 +1069,36 @@
         <v>5</v>
       </c>
       <c r="C13">
-        <v>35000000</v>
-      </c>
-      <c r="D13">
-        <v>68</v>
+        <v>25000000</v>
+      </c>
+      <c r="D13" t="str">
+        <f t="shared" si="0"/>
+        <v>2500만</v>
       </c>
       <c r="E13">
+        <v>55</v>
+      </c>
+      <c r="F13">
         <v>2800000</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="str">
+        <f t="shared" si="1"/>
+        <v>280만</v>
+      </c>
+      <c r="H13" t="s">
         <v>34</v>
       </c>
-      <c r="G13">
+      <c r="I13">
         <v>20</v>
       </c>
-      <c r="H13">
+      <c r="J13">
         <v>65</v>
       </c>
-      <c r="I13">
+      <c r="K13">
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -986,28 +1106,36 @@
         <v>10</v>
       </c>
       <c r="C14">
-        <v>90000000</v>
-      </c>
-      <c r="D14">
-        <v>65</v>
+        <v>40000000</v>
+      </c>
+      <c r="D14" t="str">
+        <f t="shared" si="0"/>
+        <v>4000만</v>
       </c>
       <c r="E14">
+        <v>50</v>
+      </c>
+      <c r="F14">
         <v>7000000</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="str">
+        <f t="shared" si="1"/>
+        <v>700만</v>
+      </c>
+      <c r="H14" t="s">
         <v>35</v>
       </c>
-      <c r="G14">
+      <c r="I14">
         <v>30</v>
       </c>
-      <c r="H14">
+      <c r="J14">
         <v>70</v>
       </c>
-      <c r="I14">
+      <c r="K14">
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1015,31 +1143,39 @@
         <v>21</v>
       </c>
       <c r="C15">
-        <v>105000000</v>
-      </c>
-      <c r="D15">
+        <v>75000000</v>
+      </c>
+      <c r="D15" t="str">
+        <f t="shared" si="0"/>
+        <v>7500만</v>
+      </c>
+      <c r="E15">
+        <v>45</v>
+      </c>
+      <c r="F15">
+        <v>9500000</v>
+      </c>
+      <c r="G15" t="str">
+        <f t="shared" si="1"/>
+        <v>950만</v>
+      </c>
+      <c r="H15" t="s">
+        <v>36</v>
+      </c>
+      <c r="I15">
+        <v>40</v>
+      </c>
+      <c r="J15">
+        <v>80</v>
+      </c>
+      <c r="K15">
         <v>60</v>
       </c>
-      <c r="E15">
-        <v>9500000</v>
-      </c>
-      <c r="F15" t="s">
-        <v>36</v>
-      </c>
-      <c r="G15">
-        <v>40</v>
-      </c>
-      <c r="H15">
-        <v>80</v>
-      </c>
-      <c r="I15">
-        <v>60</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="L15" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1049,26 +1185,34 @@
       <c r="C16">
         <v>125200000</v>
       </c>
-      <c r="D16">
-        <v>55</v>
+      <c r="D16" t="str">
+        <f t="shared" si="0"/>
+        <v>1억 2520만</v>
       </c>
       <c r="E16">
+        <v>40</v>
+      </c>
+      <c r="F16">
         <v>12000000</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="str">
+        <f t="shared" si="1"/>
+        <v>1200만</v>
+      </c>
+      <c r="H16" t="s">
         <v>37</v>
       </c>
-      <c r="G16">
+      <c r="I16">
         <v>50</v>
       </c>
-      <c r="H16">
+      <c r="J16">
         <v>90</v>
       </c>
-      <c r="I16">
+      <c r="K16">
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1076,31 +1220,39 @@
         <v>17</v>
       </c>
       <c r="C17">
-        <v>160000000</v>
-      </c>
-      <c r="D17">
-        <v>53</v>
+        <v>250000000</v>
+      </c>
+      <c r="D17" t="str">
+        <f t="shared" si="0"/>
+        <v>2억 5000만</v>
       </c>
       <c r="E17">
+        <v>37</v>
+      </c>
+      <c r="F17">
         <v>22000000</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="str">
+        <f t="shared" si="1"/>
+        <v>2200만</v>
+      </c>
+      <c r="H17" t="s">
         <v>38</v>
       </c>
-      <c r="G17">
+      <c r="I17">
         <v>65</v>
       </c>
-      <c r="H17">
+      <c r="J17">
         <v>95</v>
       </c>
-      <c r="I17">
+      <c r="K17">
         <v>115</v>
       </c>
-      <c r="J17">
+      <c r="L17">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1108,28 +1260,36 @@
         <v>18</v>
       </c>
       <c r="C18">
-        <v>220000000</v>
-      </c>
-      <c r="D18">
-        <v>50</v>
+        <v>500000000</v>
+      </c>
+      <c r="D18" t="str">
+        <f t="shared" si="0"/>
+        <v>5억</v>
       </c>
       <c r="E18">
+        <v>30</v>
+      </c>
+      <c r="F18">
         <v>36000000</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="str">
+        <f t="shared" si="1"/>
+        <v>3600만</v>
+      </c>
+      <c r="H18" t="s">
         <v>39</v>
       </c>
-      <c r="G18">
+      <c r="I18">
         <v>80</v>
       </c>
-      <c r="H18">
+      <c r="J18">
         <v>100</v>
       </c>
-      <c r="I18">
+      <c r="K18">
         <v>130</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1137,28 +1297,36 @@
         <v>15</v>
       </c>
       <c r="C19">
-        <v>500000000</v>
-      </c>
-      <c r="D19">
-        <v>45</v>
+        <v>1500000000</v>
+      </c>
+      <c r="D19" t="str">
+        <f t="shared" si="0"/>
+        <v>15억</v>
       </c>
       <c r="E19">
+        <v>25</v>
+      </c>
+      <c r="F19">
         <v>90000000</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="str">
+        <f t="shared" si="1"/>
+        <v>9000만</v>
+      </c>
+      <c r="H19" t="s">
         <v>40</v>
       </c>
-      <c r="G19">
+      <c r="I19">
         <v>130</v>
       </c>
-      <c r="H19">
+      <c r="J19">
         <v>130</v>
       </c>
-      <c r="I19">
+      <c r="K19">
         <v>145</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1166,28 +1334,36 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>1500000000</v>
-      </c>
-      <c r="D20">
-        <v>30</v>
+        <v>5500000000</v>
+      </c>
+      <c r="D20" t="str">
+        <f t="shared" si="0"/>
+        <v>55억</v>
       </c>
       <c r="E20">
+        <v>10</v>
+      </c>
+      <c r="F20">
         <v>220000000</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="str">
+        <f t="shared" si="1"/>
+        <v>2억 2000만</v>
+      </c>
+      <c r="H20" t="s">
         <v>41</v>
       </c>
-      <c r="G20">
+      <c r="I20">
         <v>250</v>
       </c>
-      <c r="H20">
+      <c r="J20">
         <v>150</v>
       </c>
-      <c r="I20">
+      <c r="K20">
         <v>160</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1195,24 +1371,32 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>4500000000</v>
-      </c>
-      <c r="D21">
-        <v>10</v>
+        <v>30000000000</v>
+      </c>
+      <c r="D21" t="str">
+        <f t="shared" si="0"/>
+        <v>300억</v>
       </c>
       <c r="E21">
+        <v>5</v>
+      </c>
+      <c r="F21">
         <v>600000000</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="str">
+        <f t="shared" si="1"/>
+        <v>6억</v>
+      </c>
+      <c r="H21" t="s">
         <v>42</v>
       </c>
-      <c r="G21">
+      <c r="I21">
         <v>500</v>
       </c>
-      <c r="H21">
+      <c r="J21">
         <v>200</v>
       </c>
-      <c r="I21">
+      <c r="K21">
         <v>180</v>
       </c>
     </row>
